--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
@@ -579,9 +579,7 @@
           <t>016C</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -607,9 +605,7 @@
           <t>019B</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -649,9 +645,7 @@
           <t>025B</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>3</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -831,9 +825,7 @@
           <t>057C</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -995,9 +987,7 @@
           <t>078B</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>2</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1271,9 +1261,7 @@
           <t>114B</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>2</v>
-      </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -1297,9 +1285,7 @@
           <t>117ABC</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>2</v>
-      </c>
+      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1426,7 +1412,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -1535,9 +1521,7 @@
           <t>146B</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>2</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -1829,9 +1813,7 @@
           <t>S21</t>
         </is>
       </c>
-      <c r="B164" t="n">
-        <v>2</v>
-      </c>
+      <c r="B164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -1925,9 +1907,7 @@
           <t>S36</t>
         </is>
       </c>
-      <c r="B175" t="n">
-        <v>3</v>
-      </c>
+      <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -2061,9 +2041,7 @@
           <t>S50</t>
         </is>
       </c>
-      <c r="B191" t="n">
-        <v>3</v>
-      </c>
+      <c r="B191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -2225,9 +2203,7 @@
           <t>S69</t>
         </is>
       </c>
-      <c r="B210" t="n">
-        <v>2</v>
-      </c>
+      <c r="B210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
@@ -579,7 +579,9 @@
           <t>016C</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -605,7 +607,9 @@
           <t>019B</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -645,7 +649,9 @@
           <t>025B</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -987,7 +993,9 @@
           <t>078B</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1285,7 +1293,9 @@
           <t>117ABC</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1412,7 +1422,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -1521,7 +1531,9 @@
           <t>146B</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -1907,7 +1919,9 @@
           <t>S36</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="B175" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/artifacts/02_updated_data.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -579,9 +579,7 @@
           <t>016C</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -597,9 +595,7 @@
           <t>018A</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -607,9 +603,7 @@
           <t>019B</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -649,9 +643,7 @@
           <t>025B</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>3</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -704,7 +696,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -732,7 +724,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -868,7 +860,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -888,7 +880,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -906,7 +898,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -993,9 +985,7 @@
           <t>078B</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>2</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1115,9 +1105,7 @@
           <t>094C</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>1</v>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1141,9 +1129,7 @@
           <t>097ABC</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>3</v>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1152,7 +1138,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -1293,9 +1279,7 @@
           <t>117ABC</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>2</v>
-      </c>
+      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1422,7 +1406,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -1489,9 +1473,7 @@
           <t>141B</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>2</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -1531,9 +1513,7 @@
           <t>146B</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>2</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -1688,7 +1668,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -1919,9 +1899,7 @@
           <t>S36</t>
         </is>
       </c>
-      <c r="B175" t="n">
-        <v>3</v>
-      </c>
+      <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -1929,9 +1907,7 @@
           <t>S37</t>
         </is>
       </c>
-      <c r="B176" t="n">
-        <v>3</v>
-      </c>
+      <c r="B176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -1940,7 +1916,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -1950,7 +1926,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -2063,9 +2039,7 @@
           <t>S51</t>
         </is>
       </c>
-      <c r="B192" t="n">
-        <v>2</v>
-      </c>
+      <c r="B192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -2226,7 +2200,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -2286,7 +2260,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
